--- a/Stock Selection/CASH OPERATION.xlsx
+++ b/Stock Selection/CASH OPERATION.xlsx
@@ -1453,63 +1453,63 @@
     <row r="37">
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="n">
-        <v>897224221</v>
+        <v>743536649</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>45876.70314701389</v>
+        <v>45726.37542525463</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.3/1.3 @ 23.88</t>
+          <t>Profit of position #1393281432</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>4.59</v>
+        <v>0.21</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="n">
-        <v>897224252</v>
+        <v>743536650</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>45876.70315915509</v>
+        <v>45726.3754252662</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Profit of position #1554741910</t>
+          <t>CLOSE BUY 1/1.6706 @ 6.1860</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>0.42</v>
+        <v>5.98</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="n">
-        <v>897224253</v>
+        <v>897224221</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>45876.70315915509</v>
+        <v>45876.70314701389</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0495/1.3 @ 23.88</t>
+          <t>CLOSE BUY 0.3/1.3 @ 23.88</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1530,14 +1530,14 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0.76</v>
+        <v>4.59</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="n">
-        <v>897224254</v>
+        <v>897224252</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1545,11 +1545,11 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>45876.70315916667</v>
+        <v>45876.70315915509</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Profit of position #1554741956</t>
+          <t>Profit of position #1554741910</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1558,14 +1558,14 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>8.16</v>
+        <v>0.42</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="n">
-        <v>897224255</v>
+        <v>897224253</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1573,11 +1573,11 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>45876.70315916667</v>
+        <v>45876.70315915509</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.9505/1.3 @ 23.88</t>
+          <t>CLOSE BUY 0.0495/1.3 @ 23.88</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1586,14 +1586,14 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>14.54</v>
+        <v>0.76</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="n">
-        <v>897224772</v>
+        <v>897224254</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1601,27 +1601,27 @@
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>45876.7035862037</v>
+        <v>45876.70315916667</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Profit of position #1776193271</t>
+          <t>Profit of position #1554741956</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3.22</v>
+        <v>8.16</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="n">
-        <v>897224773</v>
+        <v>897224255</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1629,27 +1629,27 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>45876.7035862037</v>
+        <v>45876.70315916667</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.6724/0.8 @ 19.66</t>
+          <t>CLOSE BUY 0.9505/1.3 @ 23.88</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>10</v>
+        <v>14.54</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="n">
-        <v>897224774</v>
+        <v>897224772</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1657,11 +1657,11 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>45876.70358622685</v>
+        <v>45876.7035862037</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Profit of position #1796453499</t>
+          <t>Profit of position #1776193271</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1670,126 +1670,126 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0.52</v>
+        <v>3.22</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="n">
-        <v>897224775</v>
+        <v>743538255</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>45876.70358622685</v>
+        <v>45726.37549795139</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1276/0.8 @ 19.66</t>
+          <t>Profit of position #1393281260</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BCS</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1.99</v>
+        <v>0.3</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="n">
-        <v>897225573</v>
+        <v>743538256</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>45876.7043577662</v>
+        <v>45726.37549795139</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Profit of position #1811475646</t>
+          <t>CLOSE BUY 1.4632/2.9908 @ 6.0200</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2.8</v>
+        <v>8.51</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="n">
-        <v>897225574</v>
+        <v>743538257</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>45876.7043577662</v>
+        <v>45726.37549796296</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.8256/1 @ 15.465</t>
+          <t>Profit of position #1393287040</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11.96</v>
+        <v>0.06</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="n">
-        <v>897225575</v>
+        <v>743538259</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>45876.70435778935</v>
+        <v>45726.37549796296</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Profit of position #1845429956</t>
+          <t>CLOSE BUY 0.2503/2.9908 @ 6.0200</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.49</v>
+        <v>1.45</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="n">
-        <v>897225576</v>
+        <v>897224773</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1797,27 +1797,27 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>45876.70435778935</v>
+        <v>45876.7035862037</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1744/1 @ 15.465</t>
+          <t>CLOSE BUY 0.6724/0.8 @ 19.66</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>BBVA.MC</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2.63</v>
+        <v>10</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="n">
-        <v>897225865</v>
+        <v>897224774</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1825,27 +1825,27 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>45876.70451978009</v>
+        <v>45876.70358622685</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Profit of position #1422773288</t>
+          <t>Profit of position #1796453499</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>5.75</v>
+        <v>0.52</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="n">
-        <v>897225866</v>
+        <v>897224775</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1853,27 +1853,27 @@
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>45876.70451979167</v>
+        <v>45876.70358622685</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.483/0.5 @ 63.15</t>
+          <t>CLOSE BUY 0.1276/0.8 @ 19.66</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BCS</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>24.75</v>
+        <v>1.99</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="n">
-        <v>897225867</v>
+        <v>897225573</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1881,139 +1881,139 @@
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>45876.70451980324</v>
+        <v>45876.7043577662</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Profit of position #1461331124</t>
+          <t>Profit of position #1811475646</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="n">
-        <v>897225868</v>
+        <v>743538262</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>45876.70451980324</v>
+        <v>45726.37549798611</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.017/0.5 @ 63.15</t>
+          <t>Profit of position #1403180431</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>0.87</v>
+        <v>0.05</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="n">
-        <v>897226402</v>
+        <v>743538263</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>45876.70499892361</v>
+        <v>45726.37549798611</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Profit of position #1701098878</t>
+          <t>CLOSE BUY 0.2773/2.9908 @ 6.0200</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="n">
-        <v>897226403</v>
+        <v>743538266</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>45876.70499892361</v>
+        <v>45726.37549799769</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0383/0.15 @ 187.11</t>
+          <t>Profit of position #1403180445</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>5.34</v>
+        <v>0.01</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="n">
-        <v>897226404</v>
+        <v>743538267</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>45876.70499894676</v>
+        <v>45726.37549799769</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Profit of position #1712849726</t>
+          <t>CLOSE BUY 0.0092/2.9908 @ 6.0200</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>5.11</v>
+        <v>0.05</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="n">
-        <v>897226405</v>
+        <v>897225574</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2021,27 +2021,27 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>45876.70499894676</v>
+        <v>45876.7043577662</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0861/0.15 @ 187.11</t>
+          <t>CLOSE BUY 0.8256/1 @ 15.465</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>11</v>
+        <v>11.96</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="n">
-        <v>897226406</v>
+        <v>897225575</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2049,27 +2049,27 @@
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>45876.70499895833</v>
+        <v>45876.70435778935</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Profit of position #1806978791</t>
+          <t>Profit of position #1845429956</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.54</v>
+        <v>0.49</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="n">
-        <v>897226407</v>
+        <v>897225576</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2077,27 +2077,27 @@
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>45876.70499895833</v>
+        <v>45876.70435778935</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0256/0.15 @ 187.11</t>
+          <t>CLOSE BUY 0.1744/1 @ 15.465</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>BBVA.MC</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="n">
-        <v>897227347</v>
+        <v>897225865</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2105,83 +2105,83 @@
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>45876.7055049074</v>
+        <v>45876.70451978009</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Profit of position #1867462173</t>
+          <t>Profit of position #1422773288</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.69</v>
+        <v>5.75</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="n">
-        <v>897227348</v>
+        <v>743548157</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>45876.7055049074</v>
+        <v>45726.37603739584</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.12 @ 92.10</t>
+          <t>Profit of position #1393735509</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>9.359999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="n">
-        <v>897227962</v>
+        <v>743548158</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>45876.70596043982</v>
+        <v>45726.37603739584</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Profit of position #1450043624</t>
+          <t>CLOSE BUY 0.0366/0.2569 @ 71.160</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>-0.27</v>
+        <v>2.47</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="n">
-        <v>897227963</v>
+        <v>897225866</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2189,27 +2189,27 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>45876.70596043982</v>
+        <v>45876.70451979167</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0231/0.5555 @ 136.13</t>
+          <t>CLOSE BUY 0.483/0.5 @ 63.15</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>3.41</v>
+        <v>24.75</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="n">
-        <v>897227964</v>
+        <v>897225867</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>45876.70596045139</v>
+        <v>45876.70451980324</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Profit of position #1481609355</t>
+          <t>Profit of position #1461331124</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>-0.43</v>
+        <v>0.2</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="n">
-        <v>897227965</v>
+        <v>743548159</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>45876.70596045139</v>
+        <v>45726.37603741898</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.107/0.5555 @ 136.13</t>
+          <t>Profit of position #1395218355</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>15</v>
+        <v>0.3</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="n">
-        <v>897227966</v>
+        <v>743548160</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>45876.70596047454</v>
+        <v>45726.37603741898</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Profit of position #1559803984</t>
+          <t>CLOSE BUY 0.074/0.2569 @ 71.160</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>-0.35</v>
+        <v>4.97</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="n">
-        <v>897227967</v>
+        <v>897225868</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2301,27 +2301,27 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>45876.70596047454</v>
+        <v>45876.70451980324</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1076/0.5555 @ 136.13</t>
+          <t>CLOSE BUY 0.017/0.5 @ 63.15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>15</v>
+        <v>0.87</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="n">
-        <v>897227968</v>
+        <v>897226402</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2329,195 +2329,195 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>45876.70596048611</v>
+        <v>45876.70499892361</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Profit of position #1644789287</t>
+          <t>Profit of position #1701098878</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>0.58</v>
+        <v>1.83</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="n">
-        <v>897227969</v>
+        <v>743548161</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>45876.70596048611</v>
+        <v>45726.37603743056</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0813/0.5555 @ 136.13</t>
+          <t>Profit of position #1403166009</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>10.49</v>
+        <v>0.12</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="n">
-        <v>897227970</v>
+        <v>743548162</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>45876.70596049768</v>
+        <v>45726.37603743056</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Profit of position #1648733962</t>
+          <t>CLOSE BUY 0.0362/0.2569 @ 71.160</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>0.54</v>
+        <v>2.46</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="n">
-        <v>897227971</v>
+        <v>743548163</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>45876.70596049768</v>
+        <v>45726.37603744213</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.081/0.5555 @ 136.13</t>
+          <t>Profit of position #1403177543</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>10.49</v>
+        <v>0.12</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="n">
-        <v>897227972</v>
+        <v>743548164</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>45876.70596050926</v>
+        <v>45726.37603744213</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Profit of position #1880446963</t>
+          <t>CLOSE BUY 0.0368/0.2569 @ 71.160</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>0.54</v>
+        <v>2.5</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="n">
-        <v>897227973</v>
+        <v>743548165</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>45876.70596052083</v>
+        <v>45726.3760374537</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0774/0.5555 @ 136.13</t>
+          <t>Profit of position #1403180429</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>10</v>
+        <v>0.23</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="n">
-        <v>897227974</v>
+        <v>743548166</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>45876.70596053241</v>
+        <v>45726.3760374537</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Profit of position #1895460914</t>
+          <t>CLOSE BUY 0.0733/0.2569 @ 71.160</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.63</v>
+        <v>4.99</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="n">
-        <v>897227975</v>
+        <v>897226403</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -2525,615 +2525,607 @@
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>45876.70596053241</v>
+        <v>45876.70499892361</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0781/0.5555 @ 136.13</t>
+          <t>CLOSE BUY 0.0383/0.15 @ 187.11</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>5.34</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="n">
-        <v>897989208</v>
+        <v>897226404</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>45877.48263905093</v>
+        <v>45876.70499894676</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>Profit of position #1712849726</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>0.15</v>
+        <v>5.11</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="n">
-        <v>897989209</v>
+        <v>743719828</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>45877.48263905093</v>
+        <v>45726.43231471065</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>Profit of position #1403180445</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>-0.05</v>
+        <v>0.18</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="n">
-        <v>897989210</v>
+        <v>743719829</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>45877.48263905093</v>
+        <v>45726.43231471065</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>CLOSE BUY 0.9908/2.9908 @ 6.0270</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>0.15</v>
+        <v>5.79</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="n">
-        <v>897989211</v>
+        <v>745059929</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>45877.4826390625</v>
+        <v>45727.38638332176</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>CLOSE BUY 0.1102/0.6706 @ 6.1760</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>-0.05</v>
+        <v>0.66</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="n">
-        <v>897989222</v>
+        <v>897226405</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>45877.48263907407</v>
+        <v>45876.70499894676</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>CLOSE BUY 0.0861/0.15 @ 187.11</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>0.15</v>
+        <v>11</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="n">
-        <v>897989223</v>
+        <v>897226406</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>45877.48263907407</v>
+        <v>45876.70499895833</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>Profit of position #1806978791</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>-0.05</v>
+        <v>1.54</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="n">
-        <v>897989236</v>
+        <v>745059930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>45877.48263908565</v>
+        <v>45727.38638333333</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>Profit of position #1393301698</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="n">
-        <v>897989237</v>
+        <v>745059931</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>45877.48263908565</v>
+        <v>45727.38638333333</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>CLOSE BUY 0.1401/0.6706 @ 6.1760</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>-0.05</v>
+        <v>0.84</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="n">
-        <v>897989246</v>
+        <v>745059932</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>45877.48263909722</v>
+        <v>45727.38638335648</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>Profit of position #1403180427</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="n">
-        <v>897989247</v>
+        <v>745059933</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>45877.4826391088</v>
+        <v>45727.38638335648</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>CLOSE BUY 0.4203/0.6706 @ 6.1760</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>-0.05</v>
+        <v>2.52</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="n">
-        <v>897989258</v>
+        <v>745059994</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Subaccount Transfer</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>45877.48263912037</v>
+        <v>45727.3864047338</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>ACI</t>
-        </is>
-      </c>
+          <t>Transfer from 50872299 to 50704832</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="n">
-        <v>0.15</v>
+        <v>-52.08</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="n">
-        <v>897989259</v>
+        <v>897226407</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>45877.48263912037</v>
+        <v>45876.70499895833</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>CLOSE BUY 0.0256/0.15 @ 187.11</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>-0.05</v>
+        <v>3.25</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="n">
-        <v>897989274</v>
+        <v>897227347</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>45877.48263913194</v>
+        <v>45876.7055049074</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>Profit of position #1867462173</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>0.15</v>
+        <v>1.69</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="n">
-        <v>897989275</v>
+        <v>745059928</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>45877.48263914352</v>
+        <v>45727.38638332176</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>Profit of position #1393281432</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="n">
-        <v>897989278</v>
+        <v>897227348</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>45877.48263914352</v>
+        <v>45876.7055049074</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ACI.US USD 0.1500/ SHR</t>
+          <t>CLOSE BUY 0.12 @ 92.10</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>0.15</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="n">
-        <v>897989279</v>
+        <v>897227962</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>45877.48263914352</v>
+        <v>45876.70596043982</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>ACI.US USD WHT 30%</t>
+          <t>Profit of position #1450043624</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>-0.05</v>
+        <v>-0.27</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="n">
-        <v>898007075</v>
+        <v>584485943</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Subaccount Transfer</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>45877.48890388889</v>
+        <v>45495.92558700231</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MA.US USD 0.7600/ SHR</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
+          <t>Transfer from 50704832 to 50872299</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="n">
-        <v>0.01</v>
+        <v>50</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="n">
-        <v>810480537</v>
+        <v>584584545</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>45791.64976436343</v>
+        <v>45496.3756843287</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Profit of position #1599454287</t>
+          <t>OPEN BUY 4/4.1401 @ 5.9810</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>0.03</v>
+        <v>-23.92</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="n">
-        <v>810480538</v>
+        <v>584584380</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>45791.64976436343</v>
+        <v>45496.37565851852</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0763/0.35 @ 196.89</t>
+          <t>OPEN BUY 4/4.2503 @ 5.8120</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>14.99</v>
+        <v>-23.25</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="n">
-        <v>810480539</v>
+        <v>897227963</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>45791.64976438657</v>
+        <v>45876.70596043982</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Profit of position #1621495599</t>
+          <t>CLOSE BUY 0.0231/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="n">
-        <v>810480540</v>
+        <v>584587915</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>45791.64976438657</v>
+        <v>45496.37755148148</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0817/0.35 @ 196.89</t>
+          <t>OPEN BUY 0.2503/4.2503 @ 5.8110</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>14.98</v>
+        <v>-1.45</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="n">
-        <v>810480541</v>
+        <v>897227964</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -3141,363 +3133,363 @@
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>45791.64976439815</v>
+        <v>45876.70596045139</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Profit of position #1631467534</t>
+          <t>Profit of position #1481609355</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>3.48</v>
+        <v>-0.43</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="n">
-        <v>810480542</v>
+        <v>584598125</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>45791.64976439815</v>
+        <v>45496.37886087963</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0937/0.35 @ 196.89</t>
+          <t>OPEN BUY 0.1401/4.1401 @ 5.9900</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>14.97</v>
+        <v>-0.84</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="n">
-        <v>810480543</v>
+        <v>897227965</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>45791.64976440973</v>
+        <v>45876.70596045139</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Profit of position #1666449688</t>
+          <t>CLOSE BUY 0.107/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>3.37</v>
+        <v>15</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="n">
-        <v>810480544</v>
+        <v>897227966</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>45791.64976440973</v>
+        <v>45876.70596047454</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0932/0.35 @ 196.89</t>
+          <t>Profit of position #1559803984</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>14.98</v>
+        <v>-0.35</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="n">
-        <v>810480545</v>
+        <v>584801661</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>45791.64976442129</v>
+        <v>45496.61777700231</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Profit of position #1701098878</t>
+          <t>OPEN BUY 0.0366 @ 67.370</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>0.29</v>
+        <v>-2.47</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="n">
-        <v>810480546</v>
+        <v>584801647</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>45791.64976442129</v>
+        <v>45496.61775549768</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0051/0.35 @ 196.89</t>
+          <t>Profit of position #1393281260</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="n">
-        <v>811412437</v>
+        <v>584801648</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>45792.45361672454</v>
+        <v>45496.61775549768</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AAPL.US USD 0.2600/ SHR</t>
+          <t>CLOSE BUY 0.5612 @ 5.8100</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="n">
-        <v>749122474</v>
+        <v>897227967</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>45730.481945</v>
+        <v>45876.70596047454</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>EXC.US USD 0.4000/ SHR</t>
+          <t>CLOSE BUY 0.1076/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0.09</v>
+        <v>15</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="n">
-        <v>749122475</v>
+        <v>897227968</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>45730.481945</v>
+        <v>45876.70596048611</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>EXC.US USD WHT 30%</t>
+          <t>Profit of position #1644789287</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>-0.03</v>
+        <v>0.58</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="n">
-        <v>749122538</v>
+        <v>584801643</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>45730.48194508102</v>
+        <v>45496.61775508102</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>EXC.US USD 0.4000/ SHR</t>
+          <t>Profit of position #1393281432</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0.1</v>
+        <v>-0.01</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="n">
-        <v>749122539</v>
+        <v>584801644</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>45730.48194509259</v>
+        <v>45496.61775508102</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>EXC.US USD WHT 30%</t>
+          <t>CLOSE BUY 0.632 @ 5.9670</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>-0.03</v>
+        <v>3.78</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="n">
-        <v>749122586</v>
+        <v>585465634</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>45730.48194515047</v>
+        <v>45497.6542358912</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EXC.US USD 0.4000/ SHR</t>
+          <t>OPEN BUY 0.074 @ 67.130</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>0.11</v>
+        <v>-4.97</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="n">
-        <v>749122587</v>
+        <v>897227969</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>45730.48194515047</v>
+        <v>45876.70596048611</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EXC.US USD WHT 30%</t>
+          <t>CLOSE BUY 0.0813/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>-0.03</v>
+        <v>10.49</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="n">
-        <v>705165194</v>
+        <v>897227970</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -3505,139 +3497,139 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>45680.72583967593</v>
+        <v>45876.70596049768</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Profit of position #1373744560</t>
+          <t>Profit of position #1648733962</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>-3.8</v>
+        <v>0.54</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="n">
-        <v>705165195</v>
+        <v>585465630</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>45680.72583967593</v>
+        <v>45497.65423548611</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1248/0.1928 @ 172.09</t>
+          <t>Profit of position #1393281260</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>25.28</v>
+        <v>-0.01</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="n">
-        <v>705165196</v>
+        <v>585465631</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>45680.7258396875</v>
+        <v>45497.65423548611</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Profit of position #1450039117</t>
+          <t>CLOSE BUY 0.555/1.555 @ 5.8010</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>0.71</v>
+        <v>3.23</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="n">
-        <v>705165197</v>
+        <v>585465632</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>45680.7258396875</v>
+        <v>45497.65423565972</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.068/0.1928 @ 172.09</t>
+          <t>Profit of position #1393281432</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>10.99</v>
+        <v>-0.01</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="n">
-        <v>901565948</v>
+        <v>585465633</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>45881.70511174769</v>
+        <v>45497.65423565972</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.2789 @ 35.88</t>
+          <t>CLOSE BUY 0.4344/1.4344 @ 5.9680</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>-10.01</v>
+        <v>2.6</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="n">
-        <v>812342414</v>
+        <v>585515127</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -3645,27 +3637,27 @@
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>45792.64655023148</v>
+        <v>45497.67739417824</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Profit of position #1701098878</t>
+          <t>Profit of position #1393281432</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="n">
-        <v>812342415</v>
+        <v>585515128</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -3673,111 +3665,111 @@
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>45792.64655023148</v>
+        <v>45497.67739417824</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1 @ 188.02</t>
+          <t>CLOSE BUY 1/1.4344 @ 5.9780</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>13.94</v>
+        <v>5.98</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="n">
-        <v>812344995</v>
+        <v>897227971</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>45792.64714150463</v>
+        <v>45876.70596049768</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.1548 @ 129.17</t>
+          <t>CLOSE BUY 0.081/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>-20</v>
+        <v>10.49</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="n">
-        <v>812344662</v>
+        <v>897227972</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>45792.64702016204</v>
+        <v>45876.70596050926</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OPEN BUY 1 @ 21.66</t>
+          <t>Profit of position #1880446963</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>-21.66</v>
+        <v>0.54</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="n">
-        <v>812345615</v>
+        <v>897227973</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>45792.64732983796</v>
+        <v>45876.70596052083</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.2344 @ 42.66</t>
+          <t>CLOSE BUY 0.0774/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>EXC</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>-10</v>
+        <v>10</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="n">
-        <v>812347477</v>
+        <v>897227974</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -3785,223 +3777,223 @@
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>45792.64781771991</v>
+        <v>45876.70596053241</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Profit of position #1426782063</t>
+          <t>Profit of position #1895460914</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>0.01</v>
+        <v>0.63</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="n">
-        <v>812347478</v>
+        <v>585515124</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>45792.64781771991</v>
+        <v>45497.67739378472</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0004/0.04 @ 452.34</t>
+          <t>Profit of position #1393281260</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="n">
-        <v>812347479</v>
+        <v>585515125</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>45792.64781774305</v>
+        <v>45497.67739378472</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Profit of position #1481614059</t>
+          <t>CLOSE BUY 1/1.555 @ 5.8140</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>1.27</v>
+        <v>5.81</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="n">
-        <v>812347480</v>
+        <v>589161439</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>45792.64781774305</v>
+        <v>45504.63556375</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0359/0.04 @ 452.34</t>
+          <t>Profit of position #1393281260</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>14.97</v>
+        <v>0.01</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="n">
-        <v>812347481</v>
+        <v>589161440</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>45792.64781775463</v>
+        <v>45504.63556375</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Profit of position #1517514880</t>
+          <t>CLOSE BUY 0.4206 @ 5.8260</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0.16</v>
+        <v>2.44</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="n">
-        <v>812347482</v>
+        <v>589161441</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>45792.64781775463</v>
+        <v>45504.63556420139</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0037/0.04 @ 452.34</t>
+          <t>Profit of position #1393281432</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="n">
-        <v>812348265</v>
+        <v>589161442</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>45792.64805196759</v>
+        <v>45504.63556420139</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.2641 @ 56.78</t>
+          <t>CLOSE BUY 0.4033 @ 5.9800</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>-15</v>
+        <v>2.41</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="n">
-        <v>812396911</v>
+        <v>897227975</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sec Fee</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>45792.66631618056</v>
+        <v>45876.70596053241</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sec Fee adj FSLR.US 20250514</t>
+          <t>CLOSE BUY 0.0781/0.5555 @ 136.13</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="n">
-        <v>831135799</v>
+        <v>897989208</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -4009,219 +4001,223 @@
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>45812.49236300926</v>
+        <v>45877.48263905093</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>BND.US USD 0.2403/ SHR</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="n">
-        <v>831135800</v>
+        <v>589161443</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>45812.49236300926</v>
+        <v>45504.63556431713</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>BND.US USD WHT 30%</t>
+          <t>OPEN BUY 0.0362 @ 68.050</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-2.46</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="n">
-        <v>831135811</v>
+        <v>589165770</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>45812.49236302084</v>
+        <v>45504.64158165509</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>BND.US USD 0.2403/ SHR</t>
+          <t>OPEN BUY 0.0368 @ 68.045</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>0.24</v>
+        <v>-2.5</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="n">
-        <v>831135812</v>
+        <v>589166859</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>45812.49236302084</v>
+        <v>45504.64299375</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>BND.US USD WHT 30%</t>
+          <t>OPEN BUY 0.0733 @ 68.010</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>BND</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.99</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="n">
-        <v>749767690</v>
+        <v>589165768</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>deposit</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>45730.86454212963</v>
+        <v>45504.64158157408</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>SafetyPay deposit, SafetyPay provider transaction id=0125073485538638, SafetyPay merchant reference id=254335, id=18121108</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
+          <t>Profit of position #1393281432</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>FLOA.L</t>
+        </is>
+      </c>
       <c r="G132" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="n">
-        <v>812643919</v>
+        <v>897989209</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>45792.76080336806</v>
+        <v>45877.48263905093</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.3559 @ 28.09</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AGIO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>-10</v>
+        <v>-0.05</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="n">
-        <v>812644050</v>
+        <v>589165769</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>45792.76093178241</v>
+        <v>45504.64158157408</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.2894 @ 34.55</t>
+          <t>CLOSE BUY 0.4201 @ 5.9800</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>-10</v>
+        <v>2.51</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="n">
-        <v>752507751</v>
+        <v>897989210</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>45734.8548940625</v>
+        <v>45877.48263905093</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0861 @ 127.72</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>-11</v>
+        <v>0.15</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="n">
-        <v>752508164</v>
+        <v>589166872</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -4229,39 +4225,39 @@
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>45734.8557677662</v>
+        <v>45504.64301291667</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.1244 @ 160.64</t>
+          <t>OPEN BUY 1/1.2773 @ 5.8360</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>-19.98</v>
+        <v>-5.84</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="n">
-        <v>902738653</v>
+        <v>897989211</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>45882.68269450231</v>
+        <v>45877.4826390625</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>OPEN BUY 1 @ 18.80</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4270,14 +4266,14 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>-18.8</v>
+        <v>-0.05</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="n">
-        <v>903312249</v>
+        <v>897989222</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -4285,811 +4281,811 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>45883.32652819445</v>
+        <v>45877.48263907407</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AAPL.US USD 0.2600/ SHR</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="n">
-        <v>813718072</v>
+        <v>589166858</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sec Fee</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>45793.65999416666</v>
+        <v>45504.64299368056</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Sec Fee adj FSLR.US 20250515</t>
+          <t>OPEN BUY 0.4203 @ 5.9890</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>FLOA.L</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>-2.52</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="n">
-        <v>813790252</v>
+        <v>589166860</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Sec Fee</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>45793.68157241898</v>
+        <v>45504.64299381944</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Sec Fee adj MSFT.US 20250515</t>
+          <t>OPEN BUY 0.2773/1.2773 @ 5.8400</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>SDIA.L</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="n">
-        <v>905554615</v>
+        <v>622623348</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>45884.65727969907</v>
+        <v>45560.50025998842</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0469 @ 319.83</t>
+          <t>VHYD.UK USD 0.4947/ SHR</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>-15</v>
+        <v>0.04</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="n">
-        <v>754634504</v>
+        <v>622623355</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>45737.1133778125</v>
+        <v>45560.50026001158</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Profit of position #1717095547</t>
+          <t>VHYD.UK USD 0.4947/ SHR</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>2.98</v>
+        <v>0.02</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="n">
-        <v>754634505</v>
+        <v>897989223</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>swap</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>45737.1133778125</v>
+        <v>45877.48263907407</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Swap of position #1717095547</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>MXN=X</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>-0.8</v>
+        <v>-0.05</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="n">
-        <v>905824325</v>
+        <v>897989236</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>45884.8359058912</v>
+        <v>45877.48263908565</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Profit of position #1806978791</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>4.78</v>
+        <v>0.15</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="n">
-        <v>905824326</v>
+        <v>622623917</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>45884.8359058912</v>
+        <v>45560.50026123843</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0611/0.1 @ 204.97</t>
+          <t>VHYD.UK USD 0.4947/ SHR</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>7.74</v>
+        <v>0.04</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="n">
-        <v>743536649</v>
+        <v>622625644</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>45726.37542525463</v>
+        <v>45560.50026513889</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>VHYD.UK USD 0.4947/ SHR</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>0.21</v>
+        <v>0.02</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="n">
-        <v>743536650</v>
+        <v>897989237</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>45726.3754252662</v>
+        <v>45877.48263908565</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>CLOSE BUY 1/1.6706 @ 6.1860</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>5.98</v>
+        <v>-0.05</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="n">
-        <v>905824328</v>
+        <v>897989246</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>45884.83590590278</v>
+        <v>45877.48263909722</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Profit of position #1811432805</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G148" t="n">
-        <v>2.97</v>
+        <v>0.15</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="n">
-        <v>905824329</v>
+        <v>622630052</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>45884.83590590278</v>
+        <v>45560.50027641204</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0389/0.1 @ 204.97</t>
+          <t>VHYD.UK USD 0.4947/ SHR</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G149" t="n">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="n">
-        <v>905824743</v>
+        <v>686256998</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>45884.83650790509</v>
+        <v>45653.5243162037</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Profit of position #1414752069</t>
+          <t>VHYD.UK USD 0.4296/ SHR</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G150" t="n">
-        <v>-0.38</v>
+        <v>0.03</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="n">
-        <v>743538255</v>
+        <v>686258590</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>45726.37549795139</v>
+        <v>45653.52432037037</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Profit of position #1393281260</t>
+          <t>VHYD.UK USD 0.4296/ SHR</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G151" t="n">
-        <v>0.3</v>
+        <v>0.02</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="n">
-        <v>743538256</v>
+        <v>897989247</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>45726.37549795139</v>
+        <v>45877.4826391088</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CLOSE BUY 1.4632/2.9908 @ 6.0200</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G152" t="n">
-        <v>8.51</v>
+        <v>-0.05</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="n">
-        <v>905824744</v>
+        <v>897989258</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>45884.83650790509</v>
+        <v>45877.48263912037</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1933/0.9 @ 75.59</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>14.99</v>
+        <v>0.15</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="n">
-        <v>905824745</v>
+        <v>686260561</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>45884.83650791667</v>
+        <v>45653.52432525463</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Profit of position #1559802942</t>
+          <t>VHYD.UK USD 0.4296/ SHR</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>-0.45</v>
+        <v>0.02</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="n">
-        <v>743538257</v>
+        <v>686268778</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>45726.37549796296</v>
+        <v>45653.524345</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Profit of position #1393287040</t>
+          <t>VHYD.UK USD 0.4296/ SHR</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="n">
-        <v>743538259</v>
+        <v>686269321</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>45726.37549796296</v>
+        <v>45653.52434626158</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.2503/2.9908 @ 6.0200</t>
+          <t>VHYD.UK USD 0.4296/ SHR</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>VHYD.L</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1.45</v>
+        <v>0.03</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="n">
-        <v>905824746</v>
+        <v>897989259</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>45884.83650791667</v>
+        <v>45877.48263912037</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.2585/0.9 @ 75.59</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>19.99</v>
+        <v>-0.05</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="n">
-        <v>905824747</v>
+        <v>897989274</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>45884.83650792824</v>
+        <v>45877.48263913194</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Profit of position #1662995258</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>2.25</v>
+        <v>0.15</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="n">
-        <v>905824748</v>
+        <v>897989275</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>45884.83650792824</v>
+        <v>45877.48263914352</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.2943/0.9 @ 75.59</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G159" t="n">
-        <v>20</v>
+        <v>-0.05</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="n">
-        <v>905824749</v>
+        <v>897989278</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>45884.83650793981</v>
+        <v>45877.48263914352</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Profit of position #1843468958</t>
+          <t>ACI.US USD 0.1500/ SHR</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1.17</v>
+        <v>0.15</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="n">
-        <v>743538262</v>
+        <v>897989279</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>45726.37549798611</v>
+        <v>45877.48263914352</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Profit of position #1403180431</t>
+          <t>ACI.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G161" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="n">
-        <v>905824750</v>
+        <v>898007075</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>45884.83650793981</v>
+        <v>45877.48890388889</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1539/0.9 @ 75.59</t>
+          <t>MA.US USD 0.7600/ SHR</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>NEE</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="G162" t="n">
-        <v>10.46</v>
+        <v>0.01</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
       <c r="B163" t="n">
-        <v>743538263</v>
+        <v>810480537</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>45726.37549798611</v>
+        <v>45791.64976436343</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.2773/2.9908 @ 6.0200</t>
+          <t>Profit of position #1599454287</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1.62</v>
+        <v>0.03</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
       <c r="B164" t="n">
-        <v>743538266</v>
+        <v>810480538</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>45726.37549799769</v>
+        <v>45791.64976436343</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Profit of position #1403180445</t>
+          <t>CLOSE BUY 0.0763/0.35 @ 196.89</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G164" t="n">
-        <v>0.01</v>
+        <v>14.99</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
       <c r="B165" t="n">
-        <v>743538267</v>
+        <v>810480539</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>45726.37549799769</v>
+        <v>45791.64976438657</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0092/2.9908 @ 6.0200</t>
+          <t>Profit of position #1621495599</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G165" t="n">
-        <v>0.05</v>
+        <v>1.11</v>
       </c>
       <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>
       <c r="B166" t="n">
-        <v>905825195</v>
+        <v>810480540</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>45884.83731815972</v>
+        <v>45791.64976438657</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.8064 @ 49.60</t>
+          <t>CLOSE BUY 0.0817/0.35 @ 196.89</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G166" t="n">
-        <v>-40</v>
+        <v>14.98</v>
       </c>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
       <c r="B167" t="n">
-        <v>743548157</v>
+        <v>810480541</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -5097,195 +5093,195 @@
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>45726.37603739584</v>
+        <v>45791.64976439815</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Profit of position #1393735509</t>
+          <t>Profit of position #1631467534</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G167" t="n">
-        <v>0.13</v>
+        <v>3.48</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
       <c r="B168" t="n">
-        <v>815120946</v>
+        <v>810480542</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>45796.57642055555</v>
+        <v>45791.64976439815</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>ING.US USD 0.0340/ SHR</t>
+          <t>CLOSE BUY 0.0937/0.35 @ 196.89</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G168" t="n">
-        <v>0.01</v>
+        <v>14.97</v>
       </c>
       <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
       <c r="B169" t="n">
-        <v>743548158</v>
+        <v>810480543</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>45726.37603739584</v>
+        <v>45791.64976440973</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0366/0.2569 @ 71.160</t>
+          <t>Profit of position #1666449688</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G169" t="n">
-        <v>2.47</v>
+        <v>3.37</v>
       </c>
       <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
       <c r="B170" t="n">
-        <v>815120947</v>
+        <v>810480544</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>45796.57642055555</v>
+        <v>45791.64976440973</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>ING.US USD 0.0340/ SHR</t>
+          <t>CLOSE BUY 0.0932/0.35 @ 196.89</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G170" t="n">
-        <v>0.01</v>
+        <v>14.98</v>
       </c>
       <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>
       <c r="B171" t="n">
-        <v>815120948</v>
+        <v>810480545</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>45796.57642055555</v>
+        <v>45791.64976442129</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>ING.US USD 0.0340/ SHR</t>
+          <t>Profit of position #1701098878</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G171" t="n">
-        <v>0.03</v>
+        <v>0.29</v>
       </c>
       <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
       <c r="B172" t="n">
-        <v>743548159</v>
+        <v>810480546</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>45726.37603741898</v>
+        <v>45791.64976442129</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Profit of position #1395218355</t>
+          <t>CLOSE BUY 0.0051/0.35 @ 196.89</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G172" t="n">
-        <v>0.3</v>
+        <v>0.71</v>
       </c>
       <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
       <c r="B173" t="n">
-        <v>743548160</v>
+        <v>811412437</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>45726.37603741898</v>
+        <v>45792.45361672454</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.074/0.2569 @ 71.160</t>
+          <t>AAPL.US USD 0.2600/ SHR</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G173" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
       <c r="B174" t="n">
-        <v>815120949</v>
+        <v>749122474</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -5293,55 +5289,55 @@
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>45796.57642055555</v>
+        <v>45730.481945</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ING.US USD 0.0340/ SHR</t>
+          <t>EXC.US USD 0.4000/ SHR</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G174" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
       <c r="B175" t="n">
-        <v>815120950</v>
+        <v>749122475</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>45796.57642055555</v>
+        <v>45730.481945</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>ING.US USD 0.0340/ SHR</t>
+          <t>EXC.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>
       <c r="B176" t="n">
-        <v>815120951</v>
+        <v>749122538</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -5349,251 +5345,251 @@
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>45796.57642055555</v>
+        <v>45730.48194508102</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>ING.US USD 0.0340/ SHR</t>
+          <t>EXC.US USD 0.4000/ SHR</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G176" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
       <c r="B177" t="n">
-        <v>906932346</v>
+        <v>749122539</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>45887.64704410879</v>
+        <v>45730.48194509259</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Profit of position #1811432805</t>
+          <t>EXC.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G177" t="n">
-        <v>4.05</v>
+        <v>-0.03</v>
       </c>
       <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
       <c r="B178" t="n">
-        <v>743548161</v>
+        <v>749122586</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>45726.37603743056</v>
+        <v>45730.48194515047</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Profit of position #1403166009</t>
+          <t>EXC.US USD 0.4000/ SHR</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G178" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
       <c r="B179" t="n">
-        <v>743548162</v>
+        <v>749122587</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>45726.37603743056</v>
+        <v>45730.48194515047</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0362/0.2569 @ 71.160</t>
+          <t>EXC.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2.46</v>
+        <v>-0.03</v>
       </c>
       <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
       <c r="B180" t="n">
-        <v>906932347</v>
+        <v>705165194</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>45887.64704410879</v>
+        <v>45680.72583967593</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0467/0.1 @ 215.19</t>
+          <t>Profit of position #1373744560</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="G180" t="n">
-        <v>6</v>
+        <v>-3.8</v>
       </c>
       <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>
       <c r="B181" t="n">
-        <v>906932348</v>
+        <v>705165195</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>45887.64704412037</v>
+        <v>45680.72583967593</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Profit of position #1843469729</t>
+          <t>CLOSE BUY 0.1248/0.1928 @ 172.09</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>3.11</v>
+        <v>25.28</v>
       </c>
       <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
       <c r="B182" t="n">
-        <v>906932349</v>
+        <v>705165196</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>45887.64704412037</v>
+        <v>45680.7258396875</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0533/0.1 @ 215.19</t>
+          <t>Profit of position #1450039117</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="G182" t="n">
-        <v>8.359999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
       <c r="B183" t="n">
-        <v>743548163</v>
+        <v>705165197</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>45726.37603744213</v>
+        <v>45680.7258396875</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Profit of position #1403177543</t>
+          <t>CLOSE BUY 0.068/0.1928 @ 172.09</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="G183" t="n">
-        <v>0.12</v>
+        <v>10.99</v>
       </c>
       <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
       <c r="B184" t="n">
-        <v>743548164</v>
+        <v>901565948</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>45726.37603744213</v>
+        <v>45881.70511174769</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0368/0.2569 @ 71.160</t>
+          <t>OPEN BUY 0.2789 @ 35.88</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2.5</v>
+        <v>-10.01</v>
       </c>
       <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
       <c r="B185" t="n">
-        <v>743548165</v>
+        <v>812342414</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -5601,27 +5597,27 @@
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>45726.3760374537</v>
+        <v>45792.64655023148</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Profit of position #1403180429</t>
+          <t>Profit of position #1701098878</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G185" t="n">
-        <v>0.23</v>
+        <v>4.86</v>
       </c>
       <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>
       <c r="B186" t="n">
-        <v>743548166</v>
+        <v>812342415</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -5629,83 +5625,83 @@
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>45726.3760374537</v>
+        <v>45792.64655023148</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.0733/0.2569 @ 71.160</t>
+          <t>CLOSE BUY 0.1 @ 188.02</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>4.99</v>
+        <v>13.94</v>
       </c>
       <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
       <c r="B187" t="n">
-        <v>743719828</v>
+        <v>812344995</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>45726.43231471065</v>
+        <v>45792.64714150463</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Profit of position #1403180445</t>
+          <t>OPEN BUY 0.1548 @ 129.17</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>0.18</v>
+        <v>-20</v>
       </c>
       <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
       <c r="B188" t="n">
-        <v>743719829</v>
+        <v>812344662</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>45726.43231471065</v>
+        <v>45792.64702016204</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.9908/2.9908 @ 6.0270</t>
+          <t>OPEN BUY 1 @ 21.66</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>5.79</v>
+        <v>-21.66</v>
       </c>
       <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
       <c r="B189" t="n">
-        <v>907010085</v>
+        <v>812345615</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -5713,16 +5709,16 @@
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>45887.66311907407</v>
+        <v>45792.64732983796</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0787 @ 127.06</t>
+          <t>OPEN BUY 0.2344 @ 42.66</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>INGR</t>
+          <t>EXC</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -5733,171 +5729,175 @@
     <row r="190">
       <c r="A190" t="inlineStr"/>
       <c r="B190" t="n">
-        <v>745059929</v>
+        <v>812347477</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>45727.38638332176</v>
+        <v>45792.64781771991</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1102/0.6706 @ 6.1760</t>
+          <t>Profit of position #1426782063</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G190" t="n">
-        <v>0.66</v>
+        <v>0.01</v>
       </c>
       <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>
       <c r="B191" t="n">
-        <v>745059930</v>
+        <v>812347478</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>45727.38638333333</v>
+        <v>45792.64781771991</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Profit of position #1393301698</t>
+          <t>CLOSE BUY 0.0004/0.04 @ 452.34</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
       <c r="B192" t="n">
-        <v>745059931</v>
+        <v>812347479</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>45727.38638333333</v>
+        <v>45792.64781774305</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.1401/0.6706 @ 6.1760</t>
+          <t>Profit of position #1481614059</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>0.84</v>
+        <v>1.27</v>
       </c>
       <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
       <c r="B193" t="n">
-        <v>745059932</v>
+        <v>812347480</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>45727.38638335648</v>
+        <v>45792.64781774305</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Profit of position #1403180427</t>
+          <t>CLOSE BUY 0.0359/0.04 @ 452.34</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G193" t="n">
-        <v>0.08</v>
+        <v>14.97</v>
       </c>
       <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
       <c r="B194" t="n">
-        <v>745059933</v>
+        <v>812347481</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>45727.38638335648</v>
+        <v>45792.64781775463</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.4203/0.6706 @ 6.1760</t>
+          <t>Profit of position #1517514880</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2.52</v>
+        <v>0.16</v>
       </c>
       <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
       <c r="B195" t="n">
-        <v>745059994</v>
+        <v>812347482</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Subaccount Transfer</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>45727.3864047338</v>
+        <v>45792.64781775463</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Transfer from 50872299 to 50704832</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr"/>
+          <t>CLOSE BUY 0.0037/0.04 @ 452.34</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
       <c r="G195" t="n">
-        <v>-52.08</v>
+        <v>1.51</v>
       </c>
       <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>
       <c r="B196" t="n">
-        <v>907010735</v>
+        <v>812348265</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -5905,191 +5905,191 @@
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>45887.66346225695</v>
+        <v>45792.64805196759</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>OPEN BUY 1 @ 34.58</t>
+          <t>OPEN BUY 0.2641 @ 56.78</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="G196" t="n">
-        <v>-34.58</v>
+        <v>-15</v>
       </c>
       <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
       <c r="B197" t="n">
-        <v>745059928</v>
+        <v>812396911</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Sec Fee</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>45727.38638332176</v>
+        <v>45792.66631618056</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>Sec Fee adj FSLR.US 20250514</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G197" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
       <c r="B198" t="n">
-        <v>815610736</v>
+        <v>831135799</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>45796.82347</v>
+        <v>45812.49236300926</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.5793 @ 17.26</t>
+          <t>BND.US USD 0.2403/ SHR</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>-10</v>
+        <v>0.24</v>
       </c>
       <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
       <c r="B199" t="n">
-        <v>584485943</v>
+        <v>831135800</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Subaccount Transfer</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>45495.92558700231</v>
+        <v>45812.49236300926</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Transfer from 50704832 to 50872299</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr"/>
+          <t>BND.US USD WHT 30%</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>BND</t>
+        </is>
+      </c>
       <c r="G199" t="n">
-        <v>50</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
       <c r="B200" t="n">
-        <v>584584545</v>
+        <v>831135811</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D200" s="2" t="n">
-        <v>45496.3756843287</v>
+        <v>45812.49236302084</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>OPEN BUY 4/4.1401 @ 5.9810</t>
+          <t>BND.US USD 0.2403/ SHR</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="G200" t="n">
-        <v>-23.92</v>
+        <v>0.24</v>
       </c>
       <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>
       <c r="B201" t="n">
-        <v>584584380</v>
+        <v>831135812</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>45496.37565851852</v>
+        <v>45812.49236302084</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>OPEN BUY 4/4.2503 @ 5.8120</t>
+          <t>BND.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>BND</t>
         </is>
       </c>
       <c r="G201" t="n">
-        <v>-23.25</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
       <c r="B202" t="n">
-        <v>584587915</v>
+        <v>749767690</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>deposit</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>45496.37755148148</v>
+        <v>45730.86454212963</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.2503/4.2503 @ 5.8110</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>SDIA.L</t>
-        </is>
-      </c>
+          <t>SafetyPay deposit, SafetyPay provider transaction id=0125073485538638, SafetyPay merchant reference id=254335, id=18121108</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr"/>
       <c r="G202" t="n">
-        <v>-1.45</v>
+        <v>85</v>
       </c>
       <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
       <c r="B203" t="n">
-        <v>815611734</v>
+        <v>812643919</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -6097,16 +6097,16 @@
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>45796.824765625</v>
+        <v>45792.76080336806</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.297 @ 33.66</t>
+          <t>OPEN BUY 0.3559 @ 28.09</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>AGIO</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -6117,7 +6117,7 @@
     <row r="204">
       <c r="A204" t="inlineStr"/>
       <c r="B204" t="n">
-        <v>584598125</v>
+        <v>812644050</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -6125,55 +6125,55 @@
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>45496.37886087963</v>
+        <v>45792.76093178241</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.1401/4.1401 @ 5.9900</t>
+          <t>OPEN BUY 0.2894 @ 34.55</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G204" t="n">
-        <v>-0.84</v>
+        <v>-10</v>
       </c>
       <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
       <c r="B205" t="n">
-        <v>833468036</v>
+        <v>752507751</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>45814.47291704861</v>
+        <v>45734.8548940625</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>YUM.US USD 0.7100/ SHR</t>
+          <t>OPEN BUY 0.0861 @ 127.72</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>
       <c r="B206" t="n">
-        <v>584801661</v>
+        <v>752508164</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -6181,279 +6181,279 @@
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>45496.61777700231</v>
+        <v>45734.8557677662</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0366 @ 67.370</t>
+          <t>OPEN BUY 0.1244 @ 160.64</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="G206" t="n">
-        <v>-2.47</v>
+        <v>-19.98</v>
       </c>
       <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
       <c r="B207" t="n">
-        <v>584801647</v>
+        <v>902738653</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
-        <v>45496.61775549768</v>
+        <v>45882.68269450231</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Profit of position #1393281260</t>
+          <t>OPEN BUY 1 @ 18.80</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>-18.8</v>
       </c>
       <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
       <c r="B208" t="n">
-        <v>584801648</v>
+        <v>903312249</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
-        <v>45496.61775549768</v>
+        <v>45883.32652819445</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.5612 @ 5.8100</t>
+          <t>AAPL.US USD 0.2600/ SHR</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>AAPL</t>
         </is>
       </c>
       <c r="G208" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
       <c r="B209" t="n">
-        <v>908529705</v>
+        <v>813718072</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Sec Fee</t>
         </is>
       </c>
       <c r="D209" s="2" t="n">
-        <v>45888.84617736111</v>
+        <v>45793.65999416666</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0425 @ 235.53</t>
+          <t>Sec Fee adj FSLR.US 20250515</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G209" t="n">
-        <v>-10.01</v>
+        <v>0</v>
       </c>
       <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
       <c r="B210" t="n">
-        <v>584801643</v>
+        <v>813790252</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Sec Fee</t>
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>45496.61775508102</v>
+        <v>45793.68157241898</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>Sec Fee adj MSFT.US 20250515</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>
       <c r="B211" t="n">
-        <v>584801644</v>
+        <v>905554615</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>45496.61775508102</v>
+        <v>45884.65727969907</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.632 @ 5.9670</t>
+          <t>OPEN BUY 0.0469 @ 319.83</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>3.78</v>
+        <v>-15</v>
       </c>
       <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
       <c r="B212" t="n">
-        <v>585465634</v>
+        <v>754634504</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>45497.6542358912</v>
+        <v>45737.1133778125</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.074 @ 67.130</t>
+          <t>Profit of position #1717095547</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>-4.97</v>
+        <v>2.98</v>
       </c>
       <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
       <c r="B213" t="n">
-        <v>585465630</v>
+        <v>754634505</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>swap</t>
         </is>
       </c>
       <c r="D213" s="2" t="n">
-        <v>45497.65423548611</v>
+        <v>45737.1133778125</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Profit of position #1393281260</t>
+          <t>Swap of position #1717095547</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>MXN=X</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>-0.01</v>
+        <v>-0.8</v>
       </c>
       <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
       <c r="B214" t="n">
-        <v>585465631</v>
+        <v>905824325</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>45497.65423548611</v>
+        <v>45884.8359058912</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.555/1.555 @ 5.8010</t>
+          <t>Profit of position #1806978791</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G214" t="n">
-        <v>3.23</v>
+        <v>4.78</v>
       </c>
       <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
       <c r="B215" t="n">
-        <v>757003245</v>
+        <v>905824326</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>45741.42709953704</v>
+        <v>45884.8359058912</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>VWO.US USD 0.0468/ SHR</t>
+          <t>CLOSE BUY 0.0611/0.1 @ 204.97</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G215" t="n">
-        <v>0.05</v>
+        <v>7.74</v>
       </c>
       <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>
       <c r="B216" t="n">
-        <v>585465632</v>
+        <v>905824328</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -6461,27 +6461,27 @@
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>45497.65423565972</v>
+        <v>45884.83590590278</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>Profit of position #1811432805</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G216" t="n">
-        <v>-0.01</v>
+        <v>2.97</v>
       </c>
       <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
       <c r="B217" t="n">
-        <v>585465633</v>
+        <v>905824329</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -6489,27 +6489,27 @@
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>45497.65423565972</v>
+        <v>45884.83590590278</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.4344/1.4344 @ 5.9680</t>
+          <t>CLOSE BUY 0.0389/0.1 @ 204.97</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G217" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
       <c r="B218" t="n">
-        <v>585515127</v>
+        <v>905824743</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -6517,27 +6517,27 @@
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>45497.67739417824</v>
+        <v>45884.83650790509</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>Profit of position #1414752069</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
       <c r="B219" t="n">
-        <v>585515128</v>
+        <v>905824744</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -6545,27 +6545,27 @@
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>45497.67739417824</v>
+        <v>45884.83650790509</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>CLOSE BUY 1/1.4344 @ 5.9780</t>
+          <t>CLOSE BUY 0.1933/0.9 @ 75.59</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>5.98</v>
+        <v>14.99</v>
       </c>
       <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
       <c r="B220" t="n">
-        <v>585515124</v>
+        <v>905824745</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -6573,27 +6573,27 @@
         </is>
       </c>
       <c r="D220" s="2" t="n">
-        <v>45497.67739378472</v>
+        <v>45884.83650791667</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Profit of position #1393281260</t>
+          <t>Profit of position #1559802942</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>
       <c r="B221" t="n">
-        <v>585515125</v>
+        <v>905824746</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -6601,447 +6601,447 @@
         </is>
       </c>
       <c r="D221" s="2" t="n">
-        <v>45497.67739378472</v>
+        <v>45884.83650791667</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>CLOSE BUY 1/1.555 @ 5.8140</t>
+          <t>CLOSE BUY 0.2585/0.9 @ 75.59</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G221" t="n">
-        <v>5.81</v>
+        <v>19.99</v>
       </c>
       <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
       <c r="B222" t="n">
-        <v>757003246</v>
+        <v>905824747</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
-        <v>45741.42709953704</v>
+        <v>45884.83650792824</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>VWO.US USD WHT 30%</t>
+          <t>Profit of position #1662995258</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G222" t="n">
-        <v>-0.02</v>
+        <v>2.25</v>
       </c>
       <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
       <c r="B223" t="n">
-        <v>757003247</v>
+        <v>905824748</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
-        <v>45741.42709953704</v>
+        <v>45884.83650792824</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>VWO.US USD 0.0468/ SHR</t>
+          <t>CLOSE BUY 0.2943/0.9 @ 75.59</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>0.05</v>
+        <v>20</v>
       </c>
       <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
       <c r="B224" t="n">
-        <v>757003248</v>
+        <v>905824749</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D224" s="2" t="n">
-        <v>45741.42709954861</v>
+        <v>45884.83650793981</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>VWO.US USD WHT 30%</t>
+          <t>Profit of position #1843468958</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G224" t="n">
-        <v>-0.02</v>
+        <v>1.17</v>
       </c>
       <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
       <c r="B225" t="n">
-        <v>909217748</v>
+        <v>905824750</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D225" s="2" t="n">
-        <v>45889.64851538194</v>
+        <v>45884.83650793981</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.033 @ 303.76</t>
+          <t>CLOSE BUY 0.1539/0.9 @ 75.59</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>NEE</t>
         </is>
       </c>
       <c r="G225" t="n">
-        <v>-10.02</v>
+        <v>10.46</v>
       </c>
       <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>
       <c r="B226" t="n">
-        <v>589161439</v>
+        <v>905825195</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D226" s="2" t="n">
-        <v>45504.63556375</v>
+        <v>45884.83731815972</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Profit of position #1393281260</t>
+          <t>OPEN BUY 0.8064 @ 49.60</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="G226" t="n">
-        <v>0.01</v>
+        <v>-40</v>
       </c>
       <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
       <c r="B227" t="n">
-        <v>589161440</v>
+        <v>815120946</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>45504.63556375</v>
+        <v>45796.57642055555</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.4206 @ 5.8260</t>
+          <t>ING.US USD 0.0340/ SHR</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G227" t="n">
-        <v>2.44</v>
+        <v>0.01</v>
       </c>
       <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
       <c r="B228" t="n">
-        <v>589161441</v>
+        <v>815120947</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D228" s="2" t="n">
-        <v>45504.63556420139</v>
+        <v>45796.57642055555</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>ING.US USD 0.0340/ SHR</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
       <c r="B229" t="n">
-        <v>589161442</v>
+        <v>815120948</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D229" s="2" t="n">
-        <v>45504.63556420139</v>
+        <v>45796.57642055555</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.4033 @ 5.9800</t>
+          <t>ING.US USD 0.0340/ SHR</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G229" t="n">
-        <v>2.41</v>
+        <v>0.03</v>
       </c>
       <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
       <c r="B230" t="n">
-        <v>589161443</v>
+        <v>815120949</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>45504.63556431713</v>
+        <v>45796.57642055555</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0362 @ 68.050</t>
+          <t>ING.US USD 0.0340/ SHR</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G230" t="n">
-        <v>-2.46</v>
+        <v>0.03</v>
       </c>
       <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>
       <c r="B231" t="n">
-        <v>909220810</v>
+        <v>815120950</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>45889.64957445602</v>
+        <v>45796.57642055555</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0439 @ 228.00</t>
+          <t>ING.US USD 0.0340/ SHR</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>TSM</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>-10.01</v>
+        <v>0.01</v>
       </c>
       <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
       <c r="B232" t="n">
-        <v>589165770</v>
+        <v>815120951</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D232" s="2" t="n">
-        <v>45504.64158165509</v>
+        <v>45796.57642055555</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0368 @ 68.045</t>
+          <t>ING.US USD 0.0340/ SHR</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>-2.5</v>
+        <v>0.03</v>
       </c>
       <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
       <c r="B233" t="n">
-        <v>589166859</v>
+        <v>906932346</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>45504.64299375</v>
+        <v>45887.64704410879</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0733 @ 68.010</t>
+          <t>Profit of position #1811432805</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>-4.99</v>
+        <v>4.05</v>
       </c>
       <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
       <c r="B234" t="n">
-        <v>589165768</v>
+        <v>906932347</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D234" s="2" t="n">
-        <v>45504.64158157408</v>
+        <v>45887.64704410879</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Profit of position #1393281432</t>
+          <t>CLOSE BUY 0.0467/0.1 @ 215.19</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
       <c r="B235" t="n">
-        <v>589165769</v>
+        <v>906932348</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D235" s="2" t="n">
-        <v>45504.64158157408</v>
+        <v>45887.64704412037</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.4201 @ 5.9800</t>
+          <t>Profit of position #1843469729</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>2.51</v>
+        <v>3.11</v>
       </c>
       <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
       <c r="B236" t="n">
-        <v>589166872</v>
+        <v>906932349</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>45504.64301291667</v>
+        <v>45887.64704412037</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>OPEN BUY 1/1.2773 @ 5.8360</t>
+          <t>CLOSE BUY 0.0533/0.1 @ 215.19</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>-5.84</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr"/>
       <c r="B237" t="n">
-        <v>909676555</v>
+        <v>907010085</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -7049,16 +7049,16 @@
         </is>
       </c>
       <c r="D237" s="2" t="n">
-        <v>45889.85904240741</v>
+        <v>45887.66311907407</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.3162 @ 31.61</t>
+          <t>OPEN BUY 0.0787 @ 127.06</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>INGR</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -7069,7 +7069,7 @@
     <row r="238">
       <c r="A238" t="inlineStr"/>
       <c r="B238" t="n">
-        <v>589166858</v>
+        <v>907010735</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -7077,27 +7077,27 @@
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>45504.64299368056</v>
+        <v>45887.66346225695</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.4203 @ 5.9890</t>
+          <t>OPEN BUY 1 @ 34.58</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>FLOA.L</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="G238" t="n">
-        <v>-2.52</v>
+        <v>-34.58</v>
       </c>
       <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr"/>
       <c r="B239" t="n">
-        <v>589166860</v>
+        <v>815610736</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -7105,55 +7105,55 @@
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>45504.64299381944</v>
+        <v>45796.82347</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.2773/1.2773 @ 5.8400</t>
+          <t>OPEN BUY 0.5793 @ 17.26</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>SDIA.L</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="G239" t="n">
-        <v>-1.62</v>
+        <v>-10</v>
       </c>
       <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr"/>
       <c r="B240" t="n">
-        <v>622623348</v>
+        <v>815611734</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D240" s="2" t="n">
-        <v>45560.50025998842</v>
+        <v>45796.824765625</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4947/ SHR</t>
+          <t>OPEN BUY 0.297 @ 33.66</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>DAR</t>
         </is>
       </c>
       <c r="G240" t="n">
-        <v>0.04</v>
+        <v>-10</v>
       </c>
       <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr"/>
       <c r="B241" t="n">
-        <v>622623355</v>
+        <v>833468036</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -7161,251 +7161,251 @@
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>45560.50026001158</v>
+        <v>45814.47291704861</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4947/ SHR</t>
+          <t>YUM.US USD 0.7100/ SHR</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr"/>
       <c r="B242" t="n">
-        <v>742196232</v>
+        <v>908529705</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>45723.49236192129</v>
+        <v>45888.84617736111</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>YUM.US USD 0.7100/ SHR</t>
+          <t>OPEN BUY 0.0425 @ 235.53</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>YUM</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>-10.01</v>
       </c>
       <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr"/>
       <c r="B243" t="n">
-        <v>757634903</v>
+        <v>757003245</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>close trade</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>45741.87177334491</v>
+        <v>45741.42709953704</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Profit of position #1554741910</t>
+          <t>VWO.US USD 0.0468/ SHR</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>3.05</v>
+        <v>0.05</v>
       </c>
       <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr"/>
       <c r="B244" t="n">
-        <v>622623917</v>
+        <v>757003246</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>45560.50026123843</v>
+        <v>45741.42709953704</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4947/ SHR</t>
+          <t>VWO.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr"/>
       <c r="B245" t="n">
-        <v>757634904</v>
+        <v>757003247</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Stock sale</t>
+          <t>DIVIDENT</t>
         </is>
       </c>
       <c r="D245" s="2" t="n">
-        <v>45741.87177334491</v>
+        <v>45741.42709953704</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>CLOSE BUY 0.61 @ 20.29</t>
+          <t>VWO.US USD 0.0468/ SHR</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>ING</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>9.33</v>
+        <v>0.05</v>
       </c>
       <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr"/>
       <c r="B246" t="n">
-        <v>910541956</v>
+        <v>757003248</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Stock purchase</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D246" s="2" t="n">
-        <v>45890.71798859954</v>
+        <v>45741.42709954861</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>OPEN BUY 0.0512 @ 195.52</t>
+          <t>VWO.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>FSLR</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="G246" t="n">
-        <v>-10.01</v>
+        <v>-0.02</v>
       </c>
       <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr"/>
       <c r="B247" t="n">
-        <v>622625644</v>
+        <v>909217748</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D247" s="2" t="n">
-        <v>45560.50026513889</v>
+        <v>45889.64851538194</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4947/ SHR</t>
+          <t>OPEN BUY 0.033 @ 303.76</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="G247" t="n">
-        <v>0.02</v>
+        <v>-10.02</v>
       </c>
       <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr"/>
       <c r="B248" t="n">
-        <v>622630052</v>
+        <v>909220810</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
-        <v>45560.50027641204</v>
+        <v>45889.64957445602</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4947/ SHR</t>
+          <t>OPEN BUY 0.0439 @ 228.00</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>TSM</t>
         </is>
       </c>
       <c r="G248" t="n">
-        <v>0.02</v>
+        <v>-10.01</v>
       </c>
       <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr"/>
       <c r="B249" t="n">
-        <v>686256998</v>
+        <v>909676555</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D249" s="2" t="n">
-        <v>45653.5243162037</v>
+        <v>45889.85904240741</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4296/ SHR</t>
+          <t>OPEN BUY 0.3162 @ 31.61</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="G249" t="n">
-        <v>0.03</v>
+        <v>-10</v>
       </c>
       <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr"/>
       <c r="B250" t="n">
-        <v>686258590</v>
+        <v>742196232</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -7413,39 +7413,39 @@
         </is>
       </c>
       <c r="D250" s="2" t="n">
-        <v>45653.52432037037</v>
+        <v>45723.49236192129</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4296/ SHR</t>
+          <t>YUM.US USD 0.7100/ SHR</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>YUM</t>
         </is>
       </c>
       <c r="G250" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr"/>
       <c r="B251" t="n">
-        <v>758291256</v>
+        <v>757634903</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Sec Fee</t>
+          <t>close trade</t>
         </is>
       </c>
       <c r="D251" s="2" t="n">
-        <v>45742.60202539352</v>
+        <v>45741.87177334491</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Sec Fee adj ING.US 20250325</t>
+          <t>Profit of position #1554741910</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -7454,98 +7454,98 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr"/>
       <c r="B252" t="n">
-        <v>686260561</v>
+        <v>757634904</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock sale</t>
         </is>
       </c>
       <c r="D252" s="2" t="n">
-        <v>45653.52432525463</v>
+        <v>45741.87177334491</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4296/ SHR</t>
+          <t>CLOSE BUY 0.61 @ 20.29</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G252" t="n">
-        <v>0.02</v>
+        <v>9.33</v>
       </c>
       <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr"/>
       <c r="B253" t="n">
-        <v>911162471</v>
+        <v>910541956</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Stock purchase</t>
         </is>
       </c>
       <c r="D253" s="2" t="n">
-        <v>45891.49514140046</v>
+        <v>45890.71798859954</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>C.US USD 0.6000/ SHR</t>
+          <t>OPEN BUY 0.0512 @ 195.52</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>FSLR</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>0.08</v>
+        <v>-10.01</v>
       </c>
       <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr"/>
       <c r="B254" t="n">
-        <v>911162472</v>
+        <v>758291256</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Withholding Tax</t>
+          <t>Sec Fee</t>
         </is>
       </c>
       <c r="D254" s="2" t="n">
-        <v>45891.49514141204</v>
+        <v>45742.60202539352</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>C.US USD WHT 30%</t>
+          <t>Sec Fee adj ING.US 20250325</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>ING</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr"/>
       <c r="B255" t="n">
-        <v>911168117</v>
+        <v>911162471</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -7553,55 +7553,55 @@
         </is>
       </c>
       <c r="D255" s="2" t="n">
-        <v>45891.49930622685</v>
+        <v>45891.49514140046</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>APA.US USD 0.2500/ SHR</t>
+          <t>C.US USD 0.6000/ SHR</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G255" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr"/>
       <c r="B256" t="n">
-        <v>686268778</v>
+        <v>911162472</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>DIVIDENT</t>
+          <t>Withholding Tax</t>
         </is>
       </c>
       <c r="D256" s="2" t="n">
-        <v>45653.524345</v>
+        <v>45891.49514141204</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4296/ SHR</t>
+          <t>C.US USD WHT 30%</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr"/>
       <c r="B257" t="n">
-        <v>686269321</v>
+        <v>911168117</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -7609,20 +7609,20 @@
         </is>
       </c>
       <c r="D257" s="2" t="n">
-        <v>45653.52434626158</v>
+        <v>45891.49930622685</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>VHYD.UK USD 0.4296/ SHR</t>
+          <t>APA.US USD 0.2500/ SHR</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>VHYD.L</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="H257" t="inlineStr"/>
     </row>
